--- a/data/CS7/Market Data/CS7_market_data_2025.xlsx
+++ b/data/CS7/Market Data/CS7_market_data_2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\Market Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F2D815C-2239-4C39-83C6-4C5326DE62F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06AB6378-8498-43F2-9036-4D839132A781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="-12555" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15195" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenarios" sheetId="1" r:id="rId1"/>
@@ -2237,19 +2237,19 @@
         <v>1</v>
       </c>
       <c r="B1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1">
         <f>1/$B$1</f>
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" ref="D1:E1" si="0">1/$B$1</f>
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>

--- a/data/CS7/Market Data/CS7_market_data_2025.xlsx
+++ b/data/CS7/Market Data/CS7_market_data_2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\Market Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F2D815C-2239-4C39-83C6-4C5326DE62F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27EA1574-8298-49CE-BD3B-9A098FB7E8A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="-12555" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15195" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenarios" sheetId="1" r:id="rId1"/>
@@ -2237,19 +2237,19 @@
         <v>1</v>
       </c>
       <c r="B1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1">
         <f>1/$B$1</f>
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" ref="D1:E1" si="0">1/$B$1</f>
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>

--- a/data/CS7/Market Data/CS7_market_data_2025.xlsx
+++ b/data/CS7/Market Data/CS7_market_data_2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\Market Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27EA1574-8298-49CE-BD3B-9A098FB7E8A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00188ADB-95AC-486C-84B6-0C5F1C7EA839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15195" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40350" yWindow="-9285" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenarios" sheetId="1" r:id="rId1"/>

--- a/data/CS7/Market Data/CS7_market_data_2025.xlsx
+++ b/data/CS7/Market Data/CS7_market_data_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\Market Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00188ADB-95AC-486C-84B6-0C5F1C7EA839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EBEB430-9253-4A3C-B03B-3EBDCEA04694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40350" yWindow="-9285" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15195" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenarios" sheetId="1" r:id="rId1"/>
@@ -2237,19 +2237,19 @@
         <v>1</v>
       </c>
       <c r="B1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1">
         <f>1/$B$1</f>
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" ref="D1:E1" si="0">1/$B$1</f>
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>

--- a/data/CS7/Market Data/CS7_market_data_2025.xlsx
+++ b/data/CS7/Market Data/CS7_market_data_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\Market Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EBEB430-9253-4A3C-B03B-3EBDCEA04694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8019B2-FA0B-417F-B539-262AB9938EA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-15195" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2237,19 +2237,19 @@
         <v>1</v>
       </c>
       <c r="B1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1">
         <f>1/$B$1</f>
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" ref="D1:E1" si="0">1/$B$1</f>
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>

--- a/data/CS7/Market Data/CS7_market_data_2025.xlsx
+++ b/data/CS7/Market Data/CS7_market_data_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\Market Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8019B2-FA0B-417F-B539-262AB9938EA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2F5F9A-BC28-45FD-865A-6613F49C44FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-15195" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/CS7/Market Data/CS7_market_data_2025.xlsx
+++ b/data/CS7/Market Data/CS7_market_data_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\Market Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2F5F9A-BC28-45FD-865A-6613F49C44FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5D9955A-A76F-4C1A-9918-0D00908AF1CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-15195" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2237,19 +2237,19 @@
         <v>1</v>
       </c>
       <c r="B1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1">
         <f>1/$B$1</f>
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" ref="D1:E1" si="0">1/$B$1</f>
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>

--- a/data/CS7/Market Data/CS7_market_data_2025.xlsx
+++ b/data/CS7/Market Data/CS7_market_data_2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\Market Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5D9955A-A76F-4C1A-9918-0D00908AF1CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84454AF3-C07D-4657-843A-E8DF1F6BFACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15195" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33120" yWindow="-10755" windowWidth="28800" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenarios" sheetId="1" r:id="rId1"/>

--- a/data/CS7/Market Data/CS7_market_data_2025.xlsx
+++ b/data/CS7/Market Data/CS7_market_data_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\Market Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84454AF3-C07D-4657-843A-E8DF1F6BFACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A212C005-2B93-4EA0-B5CF-80A6D700B2A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33120" yWindow="-10755" windowWidth="28800" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34575" yWindow="-12570" windowWidth="28800" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenarios" sheetId="1" r:id="rId1"/>
@@ -2237,19 +2237,19 @@
         <v>1</v>
       </c>
       <c r="B1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1">
         <f>1/$B$1</f>
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" ref="D1:E1" si="0">1/$B$1</f>
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>

--- a/data/CS7/Market Data/CS7_market_data_2025.xlsx
+++ b/data/CS7/Market Data/CS7_market_data_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\Market Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A212C005-2B93-4EA0-B5CF-80A6D700B2A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0723A37-1FAF-48BF-A963-91CD33864EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34575" yWindow="-12570" windowWidth="28800" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31920" yWindow="-11265" windowWidth="28800" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenarios" sheetId="1" r:id="rId1"/>

--- a/data/CS7/Market Data/CS7_market_data_2025.xlsx
+++ b/data/CS7/Market Data/CS7_market_data_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\Market Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0723A37-1FAF-48BF-A963-91CD33864EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D25AD1-3CD9-4440-AB68-62DE5EE099CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31920" yWindow="-11265" windowWidth="28800" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33225" yWindow="-9960" windowWidth="28800" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenarios" sheetId="1" r:id="rId1"/>
@@ -2237,19 +2237,19 @@
         <v>1</v>
       </c>
       <c r="B1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1">
         <f>1/$B$1</f>
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" ref="D1:E1" si="0">1/$B$1</f>
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>

--- a/data/CS7/Market Data/CS7_market_data_2025.xlsx
+++ b/data/CS7/Market Data/CS7_market_data_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\Market Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D25AD1-3CD9-4440-AB68-62DE5EE099CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1DE79C1-FE1F-4C69-A3AC-BBF8E7475FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33225" yWindow="-9960" windowWidth="28800" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33660" yWindow="-9525" windowWidth="28800" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenarios" sheetId="1" r:id="rId1"/>
